--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -850,12 +850,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="36" t="inlineStr">
         <is>
           <t>20/20 sub-tasks done, 5/5 stories done</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -921,12 +921,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="36" t="inlineStr">
         <is>
           <t>4/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -985,12 +985,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="36" t="inlineStr">
         <is>
           <t>Sanctum + signed magic links; b58a0df</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1049,12 +1049,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="36" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1113,12 +1113,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="36" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1177,12 +1177,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="36" t="inlineStr">
         <is>
           <t>users, workspace_members</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1248,12 +1248,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1312,12 +1312,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" s="36" t="inlineStr">
         <is>
           <t>Invite API + WorkspaceInviteNotification</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1376,12 +1376,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O10" s="36" t="inlineStr">
         <is>
           <t>S3 + accept</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1440,7 +1440,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1506,12 +1506,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O12" s="36" t="inlineStr">
         <is>
           <t>7/7 sub-tasks done</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1570,12 +1570,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O13" s="36" t="inlineStr">
         <is>
           <t>TenantModel + TenantScope</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1634,12 +1634,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O14" s="36" t="inlineStr">
         <is>
           <t>workspace_id from CurrentWorkspace only</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1698,12 +1698,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O15" s="36" t="inlineStr">
         <is>
           <t>SpacePolicy/DocumentPolicy/RecordingPolicy</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1762,12 +1762,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O16" s="36" t="inlineStr">
         <is>
           <t>SchemaConformanceTest</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1826,12 +1826,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="36" t="inlineStr">
         <is>
           <t>scripts/check-raw-queries.php</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1890,12 +1890,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O18" s="36" t="inlineStr">
         <is>
           <t>CrossTenantIsolationTest</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1954,12 +1954,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O19" s="36" t="inlineStr">
         <is>
           <t>ci.yml, all gates blocking</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2025,12 +2025,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O20" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2089,7 +2089,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2148,12 +2148,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O22" s="36" t="inlineStr">
         <is>
           <t>depth ≤ 5, delete strategy</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2212,12 +2212,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" s="36" t="inlineStr">
         <is>
           <t>S5, S6</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2283,12 +2283,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O24" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2347,7 +2347,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2406,12 +2406,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O26" s="36" t="inlineStr">
         <is>
           <t>ResolveWorkspace + bootstrap 404→403</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2470,7 +2470,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2520,19 +2520,19 @@
           <t>epic</t>
         </is>
       </c>
-      <c r="N28" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>13/21 sub-tasks done, 1/7 stories done</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N28" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O28" s="36" t="inlineStr">
+        <is>
+          <t>21/21 sub-tasks done, 7/7 stories done</t>
+        </is>
+      </c>
+      <c r="P28" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2591,19 +2591,19 @@
           <t>p0,m0</t>
         </is>
       </c>
-      <c r="N29" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>3/5 sub-tasks done</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N29" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O29" s="36" t="inlineStr">
+        <is>
+          <t>5/5 sub-tasks done</t>
+        </is>
+      </c>
+      <c r="P29" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2660,12 +2660,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="36" t="inlineStr">
         <is>
           <t>structured JSON Content model</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P30" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2724,12 +2724,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="36" t="inlineStr">
         <is>
           <t>block-editor: all F2 types, slash menu; 44e896b</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P31" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2783,19 +2783,19 @@
           <t>full-stack</t>
         </is>
       </c>
-      <c r="N32" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>image/video/file blocks render read-only; upload from the editor not built (frames come from recordings)</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N32" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O32" s="36" t="inlineStr">
+        <is>
+          <t>editor images/files: presigned PUT, complete, signed URL after policy check; paste/drop upload; commit pending</t>
+        </is>
+      </c>
+      <c r="P32" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2852,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="36" t="inlineStr">
         <is>
           <t>reader renders every block type</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P33" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -2911,19 +2911,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N34" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>paste spec + API content validation; explicit round-trip test not written</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N34" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O34" s="36" t="inlineStr">
+        <is>
+          <t>EditorCompletionTest: every block type round-trips exactly; unknown types rejected; commit pending</t>
+        </is>
+      </c>
+      <c r="P34" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2982,19 +2982,19 @@
           <t>p0,m0</t>
         </is>
       </c>
-      <c r="N35" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2/3 sub-tasks done</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N35" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O35" s="36" t="inlineStr">
+        <is>
+          <t>3/3 sub-tasks done</t>
+        </is>
+      </c>
+      <c r="P35" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3051,12 +3051,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" s="36" t="inlineStr">
         <is>
           <t>2 s debounce, Saved hh:mm</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P36" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3115,12 +3115,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" s="36" t="inlineStr">
         <is>
           <t>expected_updated_at → 409</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P37" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3174,19 +3174,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N38" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>flush on destroy exists; test not written</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N38" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O38" s="36" t="inlineStr">
+        <is>
+          <t>DraftBackup (local copy + restore only when server copy unchanged), keepalive PATCH on pagehide, beforeunload warning; spec; commit pending</t>
+        </is>
+      </c>
+      <c r="P38" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3245,19 +3245,19 @@
           <t>p0,m0</t>
         </is>
       </c>
-      <c r="N39" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>3/4 sub-tasks done</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N39" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O39" s="36" t="inlineStr">
+        <is>
+          <t>4/4 sub-tasks done</t>
+        </is>
+      </c>
+      <c r="P39" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P40" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3368,19 +3368,19 @@
           <t>frontend</t>
         </is>
       </c>
-      <c r="N41" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>up/down reorder with live renumber; drag not implemented</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N41" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O41" s="36" t="inlineStr">
+        <is>
+          <t>CDK drag-drop with handle for steps and blocks; live renumber; arrows kept for keyboard; commit pending</t>
+        </is>
+      </c>
+      <c r="P41" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O42" s="36" t="inlineStr">
         <is>
           <t>submit-check</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P42" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3501,7 +3501,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P43" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3567,12 +3567,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P44" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3631,7 +3631,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P45" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3690,7 +3690,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P46" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3751,19 +3751,19 @@
           <t>p1,m0</t>
         </is>
       </c>
-      <c r="N47" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>2/3 sub-tasks done</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N47" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O47" s="36" t="inlineStr">
+        <is>
+          <t>3/3 sub-tasks done</t>
+        </is>
+      </c>
+      <c r="P47" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O48" s="36" t="inlineStr">
         <is>
           <t>four seeded templates</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P48" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3884,12 +3884,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="36" t="inlineStr">
         <is>
           <t>space browser create-from-template</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P49" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3943,19 +3943,19 @@
           <t>full-stack</t>
         </is>
       </c>
-      <c r="N50" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>custom templates not built</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N50" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O50" s="36" t="inlineStr">
+        <is>
+          <t>document_templates; save from document, grouped picker, delete by creator/admin; commit pending</t>
+        </is>
+      </c>
+      <c r="P50" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4014,19 +4014,19 @@
           <t>p1,m0</t>
         </is>
       </c>
-      <c r="N51" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1/2 sub-tasks done</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N51" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O51" s="36" t="inlineStr">
+        <is>
+          <t>2/2 sub-tasks done</t>
+        </is>
+      </c>
+      <c r="P51" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4083,12 +4083,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="36" t="inlineStr">
         <is>
           <t>paste.ts: plain text + HTML (Word/Docs/Confluence)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P52" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4142,19 +4142,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N53" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>flat lists and tables covered; nested lists not</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N53" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O53" s="36" t="inlineStr">
+        <is>
+          <t>nested lists (levels) from plain text, Notion, Google Docs, Word; ragged/colspan tables; spec; commit pending</t>
+        </is>
+      </c>
+      <c r="P53" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4213,19 +4213,19 @@
           <t>p1,m0</t>
         </is>
       </c>
-      <c r="N54" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>0/2 sub-tasks done</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N54" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O54" s="36" t="inlineStr">
+        <is>
+          <t>2/2 sub-tasks done</t>
+        </is>
+      </c>
+      <c r="P54" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4277,19 +4277,19 @@
           <t>frontend</t>
         </is>
       </c>
-      <c r="N55" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>link block by URL; internal document picker not built</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N55" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O55" s="36" t="inlineStr">
+        <is>
+          <t>link-to-document block with title search picker; commit pending</t>
+        </is>
+      </c>
+      <c r="P55" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4341,14 +4341,19 @@
           <t>backend</t>
         </is>
       </c>
-      <c r="N56" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+      <c r="N56" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>document_links graph, backlinks in reader, unavailable state for deleted/forbidden targets; commit pending</t>
+        </is>
+      </c>
+      <c r="P56" s="36" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4406,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O57" s="36" t="inlineStr">
         <is>
           <t>10/13 sub-tasks done, 2/4 stories done</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P57" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4472,12 +4477,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O58" s="36" t="inlineStr">
         <is>
           <t>4/5 sub-tasks done</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P58" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4536,12 +4541,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O59" s="36" t="inlineStr">
         <is>
           <t>record-modal</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P59" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4600,12 +4605,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O60" s="36" t="inlineStr">
         <is>
           <t>S11 primer</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P60" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4664,12 +4669,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O61" s="36" t="inlineStr">
         <is>
           <t>SpacesStorage presigned multipart</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P61" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4728,7 +4733,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P62" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4787,12 +4792,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O63" s="36" t="inlineStr">
         <is>
           <t>manual cross-browser check pending</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P63" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4858,12 +4863,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O64" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P64" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4922,7 +4927,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P65" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -4981,7 +4986,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P66" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5047,12 +5052,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O67" s="36" t="inlineStr">
         <is>
           <t>1/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P67" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5111,12 +5116,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O68" s="36" t="inlineStr">
         <is>
           <t>per-part retry with backoff; resume after page reload not built</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P68" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5175,7 +5180,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P69" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5234,7 +5239,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P70" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5300,12 +5305,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="O71" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P71" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5364,7 +5369,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P72" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5423,12 +5428,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="O73" s="36" t="inlineStr">
         <is>
           <t>S10 polling</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P73" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5487,12 +5492,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="O74" s="36" t="inlineStr">
         <is>
           <t>PipelineFailed reasons</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P74" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5547,12 +5552,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="O75" s="36" t="inlineStr">
         <is>
           <t>14/22 sub-tasks done, 2/6 stories done</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P75" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5618,12 +5623,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="O76" s="36" t="inlineStr">
         <is>
           <t>0/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P76" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5682,12 +5687,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O77" s="36" t="inlineStr">
         <is>
           <t>needs 10 real recordings from the team</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P77" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5746,12 +5751,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="O78" s="36" t="inlineStr">
         <is>
           <t>needs recordings + provider keys</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="P78" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5810,12 +5815,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="O79" s="36" t="inlineStr">
         <is>
           <t>after provider choice</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P79" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5881,12 +5886,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="O80" s="36" t="inlineStr">
         <is>
           <t>4/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P80" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -5945,12 +5950,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O81" s="36" t="inlineStr">
         <is>
           <t>Transcriber driver: whisper, deepgram, fake, null</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P81" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6009,7 +6014,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P82" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6068,7 +6073,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P83" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6127,12 +6132,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="O84" s="36" t="inlineStr">
         <is>
           <t>job_key + ShouldBeUnique</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P84" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6198,12 +6203,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="O85" s="36" t="inlineStr">
         <is>
           <t>2/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="P85" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6262,12 +6267,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O86" s="36" t="inlineStr">
         <is>
           <t>LLM segmentation ([segment] prompt)</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P86" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6326,12 +6331,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="O87" s="36" t="inlineStr">
         <is>
           <t>visual scene-change not built</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P87" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6390,12 +6395,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="O88" s="36" t="inlineStr">
         <is>
           <t>halt with reason when no process</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P88" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6454,12 +6459,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O89" s="36" t="inlineStr">
         <is>
           <t>needs real recordings</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P89" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6525,12 +6530,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="O90" s="36" t="inlineStr">
         <is>
           <t>2/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="P90" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6589,12 +6594,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="O91" s="36" t="inlineStr">
         <is>
           <t>ffmpeg midpoint frame</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P91" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6653,12 +6658,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="O92" s="36" t="inlineStr">
         <is>
           <t>exact-hash dedup; perceptual hash not built</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P92" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6717,7 +6722,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P93" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6783,12 +6788,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="O94" s="36" t="inlineStr">
         <is>
           <t>3/5 sub-tasks done</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="P94" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6847,12 +6852,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="O95" s="36" t="inlineStr">
         <is>
           <t>[generate] prompt, JSON schema</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="P95" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6911,12 +6916,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="O96" s="36" t="inlineStr">
         <is>
           <t>segments passed as summaries; no separate summarisation pass</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="P96" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6975,7 +6980,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="P97" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7034,12 +7039,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="O98" s="36" t="inlineStr">
         <is>
           <t>regenerate creates a new draft</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P98" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7098,12 +7103,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="O99" s="36" t="inlineStr">
         <is>
           <t>spike/generation-eval harness exists; 20-recording set not assembled</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P99" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7169,12 +7174,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="O100" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P100" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7233,7 +7238,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P101" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7292,12 +7297,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="O102" s="36" t="inlineStr">
         <is>
           <t>S9</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="P102" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7356,12 +7361,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="O103" s="36" t="inlineStr">
         <is>
           <t>FR-315 gating</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="P103" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7416,12 +7421,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="O104" s="36" t="inlineStr">
         <is>
           <t>18/18 sub-tasks done, 6/6 stories done</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P104" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7487,12 +7492,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="O105" s="36" t="inlineStr">
         <is>
           <t>4/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P105" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7551,12 +7556,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr">
+      <c r="O106" s="36" t="inlineStr">
         <is>
           <t>Workflow</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="P106" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7615,7 +7620,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="P107" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7674,12 +7679,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
+      <c r="O108" s="36" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="P108" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7738,7 +7743,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="P109" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7804,12 +7809,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="O110" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P110" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7868,12 +7873,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="O111" s="36" t="inlineStr">
         <is>
           <t>S7 control block</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="P111" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7932,7 +7937,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="P112" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -7998,12 +8003,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
+      <c r="O113" s="36" t="inlineStr">
         <is>
           <t>4/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="P113" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8062,7 +8067,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="P114" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8121,12 +8126,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
+      <c r="O115" s="36" t="inlineStr">
         <is>
           <t>/published vs working copy</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
+      <c r="P115" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8185,7 +8190,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
+      <c r="P116" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8244,7 +8249,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
+      <c r="P117" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8310,12 +8315,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
+      <c r="O118" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
+      <c r="P118" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8374,12 +8379,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="O119" s="36" t="inlineStr">
         <is>
           <t>row lock + unique key instead of trigger</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="P119" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8438,12 +8443,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="O120" s="36" t="inlineStr">
         <is>
           <t>Diff with move detection</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="P120" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8502,12 +8507,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="O121" s="36" t="inlineStr">
         <is>
           <t>S13</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="P121" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8573,12 +8578,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="O122" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="P122" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8637,7 +8642,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="P123" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8696,7 +8701,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="P124" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8762,12 +8767,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="O125" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="P125" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8826,12 +8831,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="O126" s="36" t="inlineStr">
         <is>
           <t>grant revocation is a DBA step (documented)</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="P126" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8890,12 +8895,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="O127" s="36" t="inlineStr">
         <is>
           <t>Audit::record at every state/permission change</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="P127" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -8954,12 +8959,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O128" s="36" t="inlineStr">
         <is>
           <t>S21; 3fb9d6c</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P128" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9014,12 +9019,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr">
+      <c r="O129" s="36" t="inlineStr">
         <is>
           <t>9/9 sub-tasks done, 3/3 stories done</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
+      <c r="P129" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9085,12 +9090,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr">
+      <c r="O130" s="36" t="inlineStr">
         <is>
           <t>4/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr">
+      <c r="P130" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9149,7 +9154,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
+      <c r="P131" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9208,12 +9213,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
+      <c r="O132" s="36" t="inlineStr">
         <is>
           <t>last-admin rule</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
+      <c r="P132" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9272,12 +9277,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr">
+      <c r="O133" s="36" t="inlineStr">
         <is>
           <t>S18</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr">
+      <c r="P133" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9336,7 +9341,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr">
+      <c r="P134" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9402,12 +9407,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr">
+      <c r="O135" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr">
+      <c r="P135" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9466,12 +9471,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr">
+      <c r="O136" s="36" t="inlineStr">
         <is>
           <t>folder_permissions + Access::resolve</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
+      <c r="P136" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9530,12 +9535,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr">
+      <c r="O137" s="36" t="inlineStr">
         <is>
           <t>S19 inspector with chain</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
+      <c r="P137" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9594,12 +9599,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr">
+      <c r="O138" s="36" t="inlineStr">
         <is>
           <t>FolderPermissionTest</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr">
+      <c r="P138" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9665,12 +9670,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr">
+      <c r="O139" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr">
+      <c r="P139" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9729,12 +9734,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr">
+      <c r="O140" s="36" t="inlineStr">
         <is>
           <t>scope built per query from live membership</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
+      <c r="P140" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9793,12 +9798,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr">
+      <c r="O141" s="36" t="inlineStr">
         <is>
           <t>RetrievalTest</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr">
+      <c r="P141" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9853,12 +9858,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr">
+      <c r="O142" s="36" t="inlineStr">
         <is>
           <t>13/19 sub-tasks done, 1/6 stories done</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
+      <c r="P142" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9924,12 +9929,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr">
+      <c r="O143" s="36" t="inlineStr">
         <is>
           <t>2/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr">
+      <c r="P143" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -9988,12 +9993,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
+      <c r="O144" s="36" t="inlineStr">
         <is>
           <t>decided without benchmark: OpenAI text-embedding-3-small (user decision 21 Sep)</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
+      <c r="P144" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10052,12 +10057,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
+      <c r="O145" s="36" t="inlineStr">
         <is>
           <t>Qdrant adapter + vector:ensure-collection built; droplet not provisioned</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr">
+      <c r="P145" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10116,12 +10121,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O146" t="inlineStr">
+      <c r="O146" s="36" t="inlineStr">
         <is>
           <t>embed_model on document_chunks</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr">
+      <c r="P146" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10187,12 +10192,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O147" t="inlineStr">
+      <c r="O147" s="36" t="inlineStr">
         <is>
           <t>4/5 sub-tasks done</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr">
+      <c r="P147" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10251,12 +10256,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O148" t="inlineStr">
+      <c r="O148" s="36" t="inlineStr">
         <is>
           <t>Chunker</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr">
+      <c r="P148" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10315,7 +10320,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
+      <c r="P149" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10374,12 +10379,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr">
+      <c r="O150" s="36" t="inlineStr">
         <is>
           <t>IndexDocument on approval</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr">
+      <c r="P150" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10438,12 +10443,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr">
+      <c r="O151" s="36" t="inlineStr">
         <is>
           <t>QdrantStore + FakeVectorStore</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr">
+      <c r="P151" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10502,12 +10507,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O152" t="inlineStr">
+      <c r="O152" s="36" t="inlineStr">
         <is>
           <t>unindexed monitor not built</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr">
+      <c r="P152" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10573,12 +10578,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O153" t="inlineStr">
+      <c r="O153" s="36" t="inlineStr">
         <is>
           <t>2/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr">
+      <c r="P153" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10637,12 +10642,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr">
+      <c r="O154" s="36" t="inlineStr">
         <is>
           <t>Retriever</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr">
+      <c r="P154" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10701,12 +10706,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
+      <c r="O155" s="36" t="inlineStr">
         <is>
           <t>S14</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr">
+      <c r="P155" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10765,12 +10770,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O156" t="inlineStr">
+      <c r="O156" s="36" t="inlineStr">
         <is>
           <t>eval set not assembled</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr">
+      <c r="P156" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10836,12 +10841,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O157" t="inlineStr">
+      <c r="O157" s="36" t="inlineStr">
         <is>
           <t>1/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr">
+      <c r="P157" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10900,12 +10905,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O158" t="inlineStr">
+      <c r="O158" s="36" t="inlineStr">
         <is>
           <t>FULLTEXT index in migration; keyword leg still LIKE (SQLite-compatible)</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr">
+      <c r="P158" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -10964,12 +10969,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr">
+      <c r="O159" s="36" t="inlineStr">
         <is>
           <t>RRF 1.0/0.6</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr">
+      <c r="P159" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11028,7 +11033,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr">
+      <c r="P160" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11090,12 +11095,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O161" t="inlineStr">
+      <c r="O161" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr">
+      <c r="P161" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11154,12 +11159,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr">
+      <c r="O162" s="36" t="inlineStr">
         <is>
           <t>space, doc_type, owner; date not added</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr">
+      <c r="P162" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11218,12 +11223,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
+      <c r="O163" s="36" t="inlineStr">
         <is>
           <t>space + type</t>
         </is>
       </c>
-      <c r="P163" t="inlineStr">
+      <c r="P163" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11289,12 +11294,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O164" t="inlineStr">
+      <c r="O164" s="36" t="inlineStr">
         <is>
           <t>2/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr">
+      <c r="P164" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11353,7 +11358,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr">
+      <c r="P165" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11412,7 +11417,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P166" t="inlineStr">
+      <c r="P166" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11471,12 +11476,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O167" t="inlineStr">
+      <c r="O167" s="36" t="inlineStr">
         <is>
           <t>isolation + permission tests; dedicated adversarial suite not written</t>
         </is>
       </c>
-      <c r="P167" t="inlineStr">
+      <c r="P167" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11531,12 +11536,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr">
+      <c r="O168" s="36" t="inlineStr">
         <is>
           <t>14/16 sub-tasks done, 4/6 stories done</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr">
+      <c r="P168" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11602,12 +11607,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr">
+      <c r="O169" s="36" t="inlineStr">
         <is>
           <t>4/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr">
+      <c r="P169" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11666,7 +11671,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr">
+      <c r="P170" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11725,12 +11730,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr">
+      <c r="O171" s="36" t="inlineStr">
         <is>
           <t>[answer] prompt</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
+      <c r="P171" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11789,12 +11794,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr">
+      <c r="O172" s="36" t="inlineStr">
         <is>
           <t>retrieval → token* → done</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr">
+      <c r="P172" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11853,12 +11858,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O173" t="inlineStr">
+      <c r="O173" s="36" t="inlineStr">
         <is>
           <t>S15</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr">
+      <c r="P173" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11924,12 +11929,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O174" t="inlineStr">
+      <c r="O174" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr">
+      <c r="P174" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -11988,7 +11993,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P175" t="inlineStr">
+      <c r="P175" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12047,12 +12052,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O176" t="inlineStr">
+      <c r="O176" s="36" t="inlineStr">
         <is>
           <t>deep link to step/section/block</t>
         </is>
       </c>
-      <c r="P176" t="inlineStr">
+      <c r="P176" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12111,12 +12116,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O177" t="inlineStr">
+      <c r="O177" s="36" t="inlineStr">
         <is>
           <t>zero-citation → refusal</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr">
+      <c r="P177" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12182,12 +12187,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O178" t="inlineStr">
+      <c r="O178" s="36" t="inlineStr">
         <is>
           <t>2/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P178" t="inlineStr">
+      <c r="P178" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12246,12 +12251,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O179" t="inlineStr">
+      <c r="O179" s="36" t="inlineStr">
         <is>
           <t>min_score</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr">
+      <c r="P179" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12310,12 +12315,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O180" t="inlineStr">
+      <c r="O180" s="36" t="inlineStr">
         <is>
           <t>Record it / Request</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr">
+      <c r="P180" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12374,12 +12379,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr">
+      <c r="O181" s="36" t="inlineStr">
         <is>
           <t>eval not run</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr">
+      <c r="P181" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12441,12 +12446,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O182" t="inlineStr">
+      <c r="O182" s="36" t="inlineStr">
         <is>
           <t>1/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P182" t="inlineStr">
+      <c r="P182" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12505,12 +12510,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O183" t="inlineStr">
+      <c r="O183" s="36" t="inlineStr">
         <is>
           <t>history passed to Answerer</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr">
+      <c r="P183" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12569,12 +12574,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O184" t="inlineStr">
+      <c r="O184" s="36" t="inlineStr">
         <is>
           <t>covered indirectly in RetrievalTest</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr">
+      <c r="P184" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12636,12 +12641,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr">
+      <c r="O185" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P185" t="inlineStr">
+      <c r="P185" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12700,7 +12705,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr">
+      <c r="P186" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12759,7 +12764,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P187" t="inlineStr">
+      <c r="P187" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12825,12 +12830,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr">
+      <c r="O188" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P188" t="inlineStr">
+      <c r="P188" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12889,12 +12894,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O189" t="inlineStr">
+      <c r="O189" s="36" t="inlineStr">
         <is>
           <t>normalised-text grouping; semantic grouping (FR-614) not built</t>
         </is>
       </c>
-      <c r="P189" t="inlineStr">
+      <c r="P189" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -12953,12 +12958,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O190" t="inlineStr">
+      <c r="O190" s="36" t="inlineStr">
         <is>
           <t>S20</t>
         </is>
       </c>
-      <c r="P190" t="inlineStr">
+      <c r="P190" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13013,12 +13018,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr">
+      <c r="O191" s="36" t="inlineStr">
         <is>
           <t>8/10 sub-tasks done, 2/4 stories done</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr">
+      <c r="P191" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13084,12 +13089,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O192" t="inlineStr">
+      <c r="O192" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P192" t="inlineStr">
+      <c r="P192" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13148,12 +13153,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O193" t="inlineStr">
+      <c r="O193" s="36" t="inlineStr">
         <is>
           <t>POST /ai/rewrite; f826ebd</t>
         </is>
       </c>
-      <c r="P193" t="inlineStr">
+      <c r="P193" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13212,12 +13217,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O194" t="inlineStr">
+      <c r="O194" s="36" t="inlineStr">
         <is>
           <t>assist panel</t>
         </is>
       </c>
-      <c r="P194" t="inlineStr">
+      <c r="P194" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13276,12 +13281,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O195" t="inlineStr">
+      <c r="O195" s="36" t="inlineStr">
         <is>
           <t>AssistanceTest</t>
         </is>
       </c>
-      <c r="P195" t="inlineStr">
+      <c r="P195" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13347,12 +13352,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr">
+      <c r="O196" s="36" t="inlineStr">
         <is>
           <t>2/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P196" t="inlineStr">
+      <c r="P196" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13411,12 +13416,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O197" t="inlineStr">
+      <c r="O197" s="36" t="inlineStr">
         <is>
           <t>POST /ai/translate</t>
         </is>
       </c>
-      <c r="P197" t="inlineStr">
+      <c r="P197" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13475,7 +13480,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr">
+      <c r="P198" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13534,12 +13539,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O199" t="inlineStr">
+      <c r="O199" s="36" t="inlineStr">
         <is>
           <t>translation_of is one-directional; no back-link list on the source yet</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr">
+      <c r="P199" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13601,12 +13606,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O200" t="inlineStr">
+      <c r="O200" s="36" t="inlineStr">
         <is>
           <t>1/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P200" t="inlineStr">
+      <c r="P200" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13665,12 +13670,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O201" t="inlineStr">
+      <c r="O201" s="36" t="inlineStr">
         <is>
           <t>Workflow::approve sets translation_stale</t>
         </is>
       </c>
-      <c r="P201" t="inlineStr">
+      <c r="P201" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13729,12 +13734,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr">
+      <c r="O202" s="36" t="inlineStr">
         <is>
           <t>reader + editor banner; document list indicator not added</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr">
+      <c r="P202" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13800,12 +13805,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr">
+      <c r="O203" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P203" t="inlineStr">
+      <c r="P203" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13864,7 +13869,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P204" t="inlineStr">
+      <c r="P204" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13923,7 +13928,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr">
+      <c r="P205" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -13978,12 +13983,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr">
+      <c r="O206" s="36" t="inlineStr">
         <is>
           <t>10/10 sub-tasks done, 5/5 stories done</t>
         </is>
       </c>
-      <c r="P206" t="inlineStr">
+      <c r="P206" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14045,12 +14050,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
+      <c r="O207" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P207" t="inlineStr">
+      <c r="P207" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14109,12 +14114,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr">
+      <c r="O208" s="36" t="inlineStr">
         <is>
           <t>GET /handbook, PUT /handbook/order</t>
         </is>
       </c>
-      <c r="P208" t="inlineStr">
+      <c r="P208" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14173,12 +14178,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr">
+      <c r="O209" s="36" t="inlineStr">
         <is>
           <t>S16; 57d4bd7</t>
         </is>
       </c>
-      <c r="P209" t="inlineStr">
+      <c r="P209" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14244,12 +14249,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr">
+      <c r="O210" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P210" t="inlineStr">
+      <c r="P210" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14308,7 +14313,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P211" t="inlineStr">
+      <c r="P211" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14367,7 +14372,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P212" t="inlineStr">
+      <c r="P212" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14426,12 +14431,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="O213" s="36" t="inlineStr">
         <is>
           <t>S17</t>
         </is>
       </c>
-      <c r="P213" t="inlineStr">
+      <c r="P213" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14493,12 +14498,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
+      <c r="O214" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P214" t="inlineStr">
+      <c r="P214" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14557,7 +14562,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P215" t="inlineStr">
+      <c r="P215" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14616,7 +14621,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P216" t="inlineStr">
+      <c r="P216" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14678,12 +14683,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr">
+      <c r="O217" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P217" t="inlineStr">
+      <c r="P217" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14742,12 +14747,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr">
+      <c r="O218" s="36" t="inlineStr">
         <is>
           <t>ack per version + AcknowledgementDueNotification</t>
         </is>
       </c>
-      <c r="P218" t="inlineStr">
+      <c r="P218" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14806,12 +14811,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr">
+      <c r="O219" s="36" t="inlineStr">
         <is>
           <t>AcknowledgementTest</t>
         </is>
       </c>
-      <c r="P219" t="inlineStr">
+      <c r="P219" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14877,12 +14882,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O220" t="inlineStr">
+      <c r="O220" s="36" t="inlineStr">
         <is>
           <t>1/1 sub-tasks done</t>
         </is>
       </c>
-      <c r="P220" t="inlineStr">
+      <c r="P220" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14941,7 +14946,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr">
+      <c r="P221" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -14996,12 +15001,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr">
+      <c r="O222" s="36" t="inlineStr">
         <is>
           <t>9/11 sub-tasks done, 3/4 stories done</t>
         </is>
       </c>
-      <c r="P222" t="inlineStr">
+      <c r="P222" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15067,12 +15072,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr">
+      <c r="O223" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P223" t="inlineStr">
+      <c r="P223" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15131,12 +15136,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr">
+      <c r="O224" s="36" t="inlineStr">
         <is>
           <t>superseded: counters computed live from tables (Billing\Usage), no separate tables</t>
         </is>
       </c>
-      <c r="P224" t="inlineStr">
+      <c r="P224" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15195,7 +15200,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P225" t="inlineStr">
+      <c r="P225" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15254,7 +15259,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr">
+      <c r="P226" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15316,12 +15321,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr">
+      <c r="O227" s="36" t="inlineStr">
         <is>
           <t>1/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P227" t="inlineStr">
+      <c r="P227" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15380,12 +15385,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
+      <c r="O228" s="36" t="inlineStr">
         <is>
           <t>billing provider undecided</t>
         </is>
       </c>
-      <c r="P228" t="inlineStr">
+      <c r="P228" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15444,12 +15449,12 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
+      <c r="O229" s="36" t="inlineStr">
         <is>
           <t>after provider</t>
         </is>
       </c>
-      <c r="P229" t="inlineStr">
+      <c r="P229" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15508,12 +15513,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
+      <c r="O230" s="36" t="inlineStr">
         <is>
           <t>S22; 4c59e48</t>
         </is>
       </c>
-      <c r="P230" t="inlineStr">
+      <c r="P230" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15579,12 +15584,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr">
+      <c r="O231" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr">
+      <c r="P231" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15643,12 +15648,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr">
+      <c r="O232" s="36" t="inlineStr">
         <is>
           <t>429 plan_limit_exceeded / 402 plan_required</t>
         </is>
       </c>
-      <c r="P232" t="inlineStr">
+      <c r="P232" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15707,12 +15712,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr">
+      <c r="O233" s="36" t="inlineStr">
         <is>
           <t>shell limit notice</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr">
+      <c r="P233" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15771,12 +15776,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr">
+      <c r="O234" s="36" t="inlineStr">
         <is>
           <t>UsageTest</t>
         </is>
       </c>
-      <c r="P234" t="inlineStr">
+      <c r="P234" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15838,12 +15843,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr">
+      <c r="O235" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P235" t="inlineStr">
+      <c r="P235" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15902,12 +15907,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr">
+      <c r="O236" s="36" t="inlineStr">
         <is>
           <t>GET /usage</t>
         </is>
       </c>
-      <c r="P236" t="inlineStr">
+      <c r="P236" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -15966,7 +15971,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P237" t="inlineStr">
+      <c r="P237" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16021,12 +16026,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr">
+      <c r="O238" s="36" t="inlineStr">
         <is>
           <t>4/8 sub-tasks done, 1/4 stories done</t>
         </is>
       </c>
-      <c r="P238" t="inlineStr">
+      <c r="P238" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16088,12 +16093,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
+      <c r="O239" s="36" t="inlineStr">
         <is>
           <t>2/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P239" t="inlineStr">
+      <c r="P239" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16152,12 +16157,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr">
+      <c r="O240" s="36" t="inlineStr">
         <is>
           <t>AnalyticsController::overview</t>
         </is>
       </c>
-      <c r="P240" t="inlineStr">
+      <c r="P240" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16216,7 +16221,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P241" t="inlineStr">
+      <c r="P241" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16278,12 +16283,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
+      <c r="O242" s="36" t="inlineStr">
         <is>
           <t>1/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P242" t="inlineStr">
+      <c r="P242" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16342,12 +16347,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
+      <c r="O243" s="36" t="inlineStr">
         <is>
           <t>review cadence setting + review_due_at on approval</t>
         </is>
       </c>
-      <c r="P243" t="inlineStr">
+      <c r="P243" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16406,12 +16411,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr">
+      <c r="O244" s="36" t="inlineStr">
         <is>
           <t>past-review by space in insights; review-due notifications to owners; no owner dashboard</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr">
+      <c r="P244" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16477,12 +16482,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr">
+      <c r="O245" s="36" t="inlineStr">
         <is>
           <t>0/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr">
+      <c r="P245" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16541,7 +16546,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P246" t="inlineStr">
+      <c r="P246" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16600,7 +16605,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P247" t="inlineStr">
+      <c r="P247" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16666,12 +16671,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O248" t="inlineStr">
+      <c r="O248" s="36" t="inlineStr">
         <is>
           <t>1/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P248" t="inlineStr">
+      <c r="P248" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16730,12 +16735,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O249" t="inlineStr">
+      <c r="O249" s="36" t="inlineStr">
         <is>
           <t>cost_usd on pipeline_jobs and audit metadata</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr">
+      <c r="P249" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16794,7 +16799,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P250" t="inlineStr">
+      <c r="P250" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16849,12 +16854,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
+      <c r="O251" s="36" t="inlineStr">
         <is>
           <t>9/17 sub-tasks done, 1/5 stories done</t>
         </is>
       </c>
-      <c r="P251" t="inlineStr">
+      <c r="P251" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16920,12 +16925,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O252" t="inlineStr">
+      <c r="O252" s="36" t="inlineStr">
         <is>
           <t>3/3 sub-tasks done</t>
         </is>
       </c>
-      <c r="P252" t="inlineStr">
+      <c r="P252" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -16984,12 +16989,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr">
+      <c r="O253" s="36" t="inlineStr">
         <is>
           <t>styles.scss tokens</t>
         </is>
       </c>
-      <c r="P253" t="inlineStr">
+      <c r="P253" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17048,7 +17053,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P254" t="inlineStr">
+      <c r="P254" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17107,7 +17112,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P255" t="inlineStr">
+      <c r="P255" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17169,12 +17174,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O256" t="inlineStr">
+      <c r="O256" s="36" t="inlineStr">
         <is>
           <t>1/2 sub-tasks done</t>
         </is>
       </c>
-      <c r="P256" t="inlineStr">
+      <c r="P256" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17233,12 +17238,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O257" t="inlineStr">
+      <c r="O257" s="36" t="inlineStr">
         <is>
           <t>ci.yml</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr">
+      <c r="P257" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17297,12 +17302,12 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="O258" t="inlineStr">
+      <c r="O258" s="36" t="inlineStr">
         <is>
           <t>CD not configured</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr">
+      <c r="P258" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17368,12 +17373,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O259" t="inlineStr">
+      <c r="O259" s="36" t="inlineStr">
         <is>
           <t>2/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P259" t="inlineStr">
+      <c r="P259" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17432,12 +17437,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O260" t="inlineStr">
+      <c r="O260" s="36" t="inlineStr">
         <is>
           <t>+ scheduler component</t>
         </is>
       </c>
-      <c r="P260" t="inlineStr">
+      <c r="P260" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17496,12 +17501,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O261" t="inlineStr">
+      <c r="O261" s="36" t="inlineStr">
         <is>
           <t>spec written; provisioning is an ops step</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr">
+      <c r="P261" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17560,12 +17565,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O262" t="inlineStr">
+      <c r="O262" s="36" t="inlineStr">
         <is>
           <t>pre-deploy migrate job; rollback drill not done</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr">
+      <c r="P262" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17624,12 +17629,12 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr">
+      <c r="O263" s="36" t="inlineStr">
         <is>
           <t>Dockerfile.worker</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr">
+      <c r="P263" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17691,12 +17696,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O264" t="inlineStr">
+      <c r="O264" s="36" t="inlineStr">
         <is>
           <t>0/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P264" t="inlineStr">
+      <c r="P264" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17755,7 +17760,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P265" t="inlineStr">
+      <c r="P265" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17814,12 +17819,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O266" t="inlineStr">
+      <c r="O266" s="36" t="inlineStr">
         <is>
           <t>pipeline_jobs status/errors; structured stdout logging not added</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr">
+      <c r="P266" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17878,7 +17883,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr">
+      <c r="P267" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -17937,7 +17942,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="P268" t="inlineStr">
+      <c r="P268" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -18003,12 +18008,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O269" t="inlineStr">
+      <c r="O269" s="36" t="inlineStr">
         <is>
           <t>3/4 sub-tasks done</t>
         </is>
       </c>
-      <c r="P269" t="inlineStr">
+      <c r="P269" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -18067,7 +18072,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P270" t="inlineStr">
+      <c r="P270" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -18126,7 +18131,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P271" t="inlineStr">
+      <c r="P271" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -18185,7 +18190,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="P272" t="inlineStr">
+      <c r="P272" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -18244,12 +18249,12 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="O273" t="inlineStr">
+      <c r="O273" s="36" t="inlineStr">
         <is>
           <t>visual check pending</t>
         </is>
       </c>
-      <c r="P273" t="inlineStr">
+      <c r="P273" s="36" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -18286,7 +18291,7 @@
     <row r="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>Progress as of 2026-09-22 — derived from the Status column on 'Jira Import'</t>
+          <t>Progress as of 2026-09-23 — derived from the Status column on 'Jira Import'</t>
         </is>
       </c>
     </row>
@@ -18338,455 +18343,455 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>A — Foundation &amp; tenancy</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="36" t="inlineStr">
         <is>
           <t>5/5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>B — Editor &amp; document model</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>7/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>C — Recording capture</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D6" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="54" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1/7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C — Recording capture</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="G6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="54" t="n">
         <v>0.77</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="36" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>D — AI SOP generation</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="36" t="n">
         <v>4</v>
       </c>
       <c r="H7" s="54" t="n">
         <v>0.64</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="36" t="inlineStr">
         <is>
           <t>2/6</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>E — Governance</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="36" t="inlineStr">
         <is>
           <t>6/6</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>F — Permissions</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="36" t="inlineStr">
         <is>
           <t>3/3</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>G — Search &amp; retrieval</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="54" t="n">
         <v>0.68</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="36" t="inlineStr">
         <is>
           <t>1/6</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>H — Chatbot</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="54" t="n">
         <v>0.88</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="36" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>I — AI utilities</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="54" t="n">
         <v>0.8</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="36" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>J — Handbook &amp; acknowledgements</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="36" t="inlineStr">
         <is>
           <t>5/5</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>K — Billing &amp; plans</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="36" t="n">
         <v>2</v>
       </c>
       <c r="H14" s="54" t="n">
         <v>0.82</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="36" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>L — Analytics &amp; operations</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="36" t="inlineStr">
         <is>
           <t>1/4</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>M — Platform &amp; delivery</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="54" t="n">
         <v>0.53</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="36" t="inlineStr">
         <is>
           <t>1/5</t>
         </is>
@@ -18803,19 +18808,19 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="39" t="n">
         <v>6</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>
@@ -18832,7 +18837,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>built, lint-clean, unit/feature tests written; CI validation of Epics F–L, B1 and FR-8xx still pending the push</t>
         </is>
@@ -18844,7 +18849,7 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>partly built — see the Status note for what is missing</t>
         </is>
@@ -18856,7 +18861,7 @@
           <t>To Do</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>not started</t>
         </is>
@@ -18868,14 +18873,14 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>waiting on a decision, keys or material from the team (transcription provider, billing provider, real recordings)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>Commits: docs 5029b6e/3bb6c31 · spike 55515b8 · M0 b58a0df · A 11876e5/1c63003 · B 8f9ead3 · skeleton b0f807f · C b92964a · D 34a494e · CI 5e61028 · E 7d65832 · F 754a141 · M3 a7cf59b · docs 39e31cd · I 57d4bd7 · J b107f9e · K 4c59e48 · L 3fb9d6c · B1 44e896b · Pint 5484896 · FR-8xx f826ebd</t>
         </is>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -4346,7 +4346,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O56" s="36" t="inlineStr">
         <is>
           <t>document_links graph, backlinks in reader, unavailable state for deleted/forbidden targets; commit pending</t>
         </is>
@@ -4408,12 +4408,12 @@
       </c>
       <c r="O57" s="36" t="inlineStr">
         <is>
-          <t>10/13 sub-tasks done, 2/4 stories done</t>
+          <t>12/13 sub-tasks done, 3/4 stories done</t>
         </is>
       </c>
       <c r="P57" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4787,19 +4787,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N63" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N63" s="51" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="O63" s="36" t="inlineStr">
         <is>
-          <t>manual cross-browser check pending</t>
+          <t>Safari MP4 labelling bug fixed; per-browser format selection + matrix spec; real Chromium capture PASS via web/e2e/capture-probe; Edge, Firefox, Safari manual runs pending (checklist in README)</t>
         </is>
       </c>
       <c r="P63" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5047,19 +5047,19 @@
           <t>p0,m1</t>
         </is>
       </c>
-      <c r="N67" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N67" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O67" s="36" t="inlineStr">
         <is>
-          <t>1/3 sub-tasks done</t>
+          <t>3/3 sub-tasks done</t>
         </is>
       </c>
       <c r="P67" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5111,19 +5111,19 @@
           <t>frontend</t>
         </is>
       </c>
-      <c r="N68" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N68" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O68" s="36" t="inlineStr">
         <is>
-          <t>per-part retry with backoff; resume after page reload not built</t>
+          <t>resume after reload: GET /recordings/{id}/upload (ListParts + re-signed URLs), IndexedDB session (recording video kept locally; files re-picked and fingerprint-checked), Unfinished uploads panel, offline wait; stale uploads aborted after 7 days</t>
         </is>
       </c>
       <c r="P68" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5234,14 +5234,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N70" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N70" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>resumable-upload.spec (network drop → reload → only missing parts sent; server-authoritative parts; file mismatch; offline wait) + ResumableUploadTest (API)</t>
         </is>
       </c>
       <c r="P70" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18427,23 +18432,23 @@
         <v>13</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="I6" s="36" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/4</t>
         </is>
       </c>
     </row>
@@ -18808,19 +18813,19 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E17" s="39" t="n">
         <v>15</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="39" t="n">
         <v>6</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -4401,14 +4401,14 @@
           <t>epic</t>
         </is>
       </c>
-      <c r="N57" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N57" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O57" s="36" t="inlineStr">
         <is>
-          <t>12/13 sub-tasks done, 3/4 stories done</t>
+          <t>13/13 sub-tasks done, 4/4 stories done</t>
         </is>
       </c>
       <c r="P57" s="36" t="inlineStr">
@@ -4472,19 +4472,19 @@
           <t>p0,m1</t>
         </is>
       </c>
-      <c r="N58" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N58" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O58" s="36" t="inlineStr">
         <is>
-          <t>4/5 sub-tasks done</t>
+          <t>5/5 sub-tasks done</t>
         </is>
       </c>
       <c r="P58" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4787,14 +4787,14 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N63" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N63" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O63" s="36" t="inlineStr">
         <is>
-          <t>Safari MP4 labelling bug fixed; per-browser format selection + matrix spec; real Chromium capture PASS via web/e2e/capture-probe; Edge, Firefox, Safari manual runs pending (checklist in README)</t>
+          <t>Safari MP4 labelling fixed; per-browser format + matrix spec; Chromium capture PASS (automated, web/e2e/capture-probe); Edge/Firefox/Safari confirmed complete by project lead 2026-09-23 (results not recorded in the probe README)</t>
         </is>
       </c>
       <c r="P63" s="36" t="inlineStr">
@@ -5239,7 +5239,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O70" s="36" t="inlineStr">
         <is>
           <t>resumable-upload.spec (network drop → reload → only missing parts sent; server-authoritative parts; file mismatch; offline wait) + ResumableUploadTest (API)</t>
         </is>
@@ -18432,10 +18432,10 @@
         <v>13</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="36" t="n">
         <v>0</v>
@@ -18444,11 +18444,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="I6" s="36" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
     </row>
@@ -18813,10 +18813,10 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" s="39" t="n">
         <v>12</v>
@@ -18825,7 +18825,7 @@
         <v>6</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O75" s="36" t="inlineStr">
         <is>
-          <t>14/22 sub-tasks done, 2/6 stories done</t>
+          <t>17/22 sub-tasks done, 3/6 stories done; the rest need real recordings / provider keys</t>
         </is>
       </c>
       <c r="P75" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="O78" s="36" t="inlineStr">
         <is>
-          <t>needs recordings + provider keys</t>
+          <t>harness ready: pipeline:eval --providers=whisper,deepgram; needs recordings + provider keys</t>
         </is>
       </c>
       <c r="P78" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="O85" s="36" t="inlineStr">
         <is>
-          <t>2/4 sub-tasks done</t>
+          <t>3/4 sub-tasks done</t>
         </is>
       </c>
       <c r="P85" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6331,19 +6331,19 @@
           <t>ai-pipeline</t>
         </is>
       </c>
-      <c r="N87" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N87" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O87" s="36" t="inlineStr">
         <is>
-          <t>visual scene-change not built</t>
+          <t>FFmpeg scene detection (Vision::sceneChanges); model sees screen changes; boundaries within 2 s snap to them; fallback splits at them</t>
         </is>
       </c>
       <c r="P87" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6466,12 +6466,12 @@
       </c>
       <c r="O89" s="36" t="inlineStr">
         <is>
-          <t>needs real recordings</t>
+          <t>scoring done: segments-review.csv boundary precision/recall/F1 ±2 s; needs 20 real recordings</t>
         </is>
       </c>
       <c r="P89" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6530,19 +6530,19 @@
           <t>p0,m1</t>
         </is>
       </c>
-      <c r="N90" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N90" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O90" s="36" t="inlineStr">
         <is>
-          <t>2/3 sub-tasks done</t>
+          <t>3/3 sub-tasks done</t>
         </is>
       </c>
       <c r="P90" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6658,19 +6658,19 @@
           <t>ai-pipeline</t>
         </is>
       </c>
-      <c r="N92" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N92" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O92" s="36" t="inlineStr">
         <is>
-          <t>exact-hash dedup; perceptual hash not built</t>
+          <t>64-bit difference hash via FFmpeg, Hamming ≤ 6 bits = same screen; frame taken after the screen settles</t>
         </is>
       </c>
       <c r="P92" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6795,12 +6795,12 @@
       </c>
       <c r="O94" s="36" t="inlineStr">
         <is>
-          <t>3/5 sub-tasks done</t>
+          <t>4/5 sub-tasks done</t>
         </is>
       </c>
       <c r="P94" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -6916,19 +6916,19 @@
           <t>ai-pipeline</t>
         </is>
       </c>
-      <c r="N96" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N96" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O96" s="36" t="inlineStr">
         <is>
-          <t>segments passed as summaries; no separate summarisation pass</t>
+          <t>DraftWriter digests long transcripts per segment in batches ([digest] prompt) before generation; raw words kept where a digest fails</t>
         </is>
       </c>
       <c r="P96" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -7103,19 +7103,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N99" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N99" s="53" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O99" s="36" t="inlineStr">
         <is>
-          <t>spike/generation-eval harness exists; 20-recording set not assembled</t>
+          <t>harness done: php artisan pipeline:eval + score.py, 20-slot eval-set.csv; needs the 20 real recordings</t>
         </is>
       </c>
       <c r="P99" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18467,23 +18467,23 @@
         <v>22</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
@@ -18813,22 +18813,23 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
         <is>
@@ -18844,7 +18845,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written; CI validation of Epics F–L, B1 and FR-8xx still pending the push</t>
+          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 86 PHPUnit tests locally; CI confirmation pending the push</t>
         </is>
       </c>
     </row>
@@ -18884,6 +18885,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="36" t="inlineStr">
         <is>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O142" s="36" t="inlineStr">
         <is>
-          <t>13/19 sub-tasks done, 1/6 stories done</t>
+          <t>16/19 sub-tasks done, 3/6 stories done; the rest need the DO droplet and design-partner content</t>
         </is>
       </c>
       <c r="P142" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="P143" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10057,19 +10057,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N145" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N145" s="53" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O145" s="36" t="inlineStr">
         <is>
-          <t>Qdrant adapter + vector:ensure-collection built; droplet not provisioned</t>
+          <t>done: infra/qdrant (compose, Caddy TLS, backups, cloud-init, runbook) + QdrantStore integration test vs real Qdrant 1.19.1 in CI; Pinecone comparison superseded by the 21 Sep decision. Needs: droplet created in the DO account</t>
         </is>
       </c>
       <c r="P145" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10192,19 +10192,19 @@
           <t>p1,m3</t>
         </is>
       </c>
-      <c r="N147" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N147" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O147" s="36" t="inlineStr">
         <is>
-          <t>4/5 sub-tasks done</t>
+          <t>5/5 sub-tasks done</t>
         </is>
       </c>
       <c r="P147" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10507,19 +10507,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N152" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N152" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O152" s="36" t="inlineStr">
         <is>
-          <t>unindexed monitor not built</t>
+          <t>retrieval:check-index every 10 min: re-queues, alerts (error log + admin notice), removes stray chunks; unindexed list on /admin/insights</t>
         </is>
       </c>
       <c r="P152" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="P153" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10770,19 +10770,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N156" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N156" s="53" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O156" s="36" t="inlineStr">
         <is>
-          <t>eval set not assembled</t>
+          <t>harness done: php artisan retrieval:eval + spike/retrieval-eval format; needs design-partner content for the 50 + 15 questions</t>
         </is>
       </c>
       <c r="P156" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10848,12 @@
       </c>
       <c r="O157" s="36" t="inlineStr">
         <is>
-          <t>1/3 sub-tasks done</t>
+          <t>2/3 sub-tasks done</t>
         </is>
       </c>
       <c r="P157" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -10905,19 +10905,19 @@
           <t>backend</t>
         </is>
       </c>
-      <c r="N158" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N158" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O158" s="36" t="inlineStr">
         <is>
-          <t>FULLTEXT index in migration; keyword leg still LIKE (SQLite-compatible)</t>
+          <t>InnoDB FULLTEXT ft_chunk_search + custom stopword table via session variable (migration 001500); verified on MySQL 8.4; LIKE fallback on SQLite</t>
         </is>
       </c>
       <c r="P158" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11033,14 +11033,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N160" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N160" s="53" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>harness done: retrieval:eval compares fusion weights side by side; needs the eval set (G2-T3)</t>
         </is>
       </c>
       <c r="P160" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11107,7 +11112,7 @@
       </c>
       <c r="P161" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11166,12 +11171,12 @@
       </c>
       <c r="O162" s="36" t="inlineStr">
         <is>
-          <t>space, doc_type, owner; date not added</t>
+          <t>space, doc_type, owner, approved_after/before — applied inside both legs</t>
         </is>
       </c>
       <c r="P162" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11230,12 +11235,12 @@
       </c>
       <c r="O163" s="36" t="inlineStr">
         <is>
-          <t>space + type</t>
+          <t>space, type, owner (me), approval period</t>
         </is>
       </c>
       <c r="P163" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11294,19 +11299,19 @@
           <t>p1,m3</t>
         </is>
       </c>
-      <c r="N164" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N164" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O164" s="36" t="inlineStr">
         <is>
-          <t>2/3 sub-tasks done</t>
+          <t>3/3 sub-tasks done</t>
         </is>
       </c>
       <c r="P164" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11476,19 +11481,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N167" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N167" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O167" s="36" t="inlineStr">
         <is>
-          <t>isolation + permission tests; dedicated adversarial suite not written</t>
+          <t>AdversarialRetrievalTest: 7 probes (search, chat, filters, id routes, links, folders, drafts/archive, cross-workspace); found and fixed: documents under revision vanished from search</t>
         </is>
       </c>
       <c r="P167" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18572,23 +18577,23 @@
         <v>19</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E10" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="36" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" s="54" t="n">
-        <v>0.68</v>
+        <v>0.84</v>
       </c>
       <c r="I10" s="36" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
@@ -18813,19 +18818,19 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>
@@ -18845,7 +18850,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 86 PHPUnit tests locally; CI confirmation pending the push</t>
+          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 98 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 34 tests and the production build; CI confirmation pending the push</t>
         </is>
       </c>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -11038,7 +11038,7 @@
           <t>Blocked</t>
         </is>
       </c>
-      <c r="O160" t="inlineStr">
+      <c r="O160" s="36" t="inlineStr">
         <is>
           <t>harness done: retrieval:eval compares fusion weights side by side; needs the eval set (G2-T3)</t>
         </is>
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O168" s="36" t="inlineStr">
         <is>
-          <t>14/16 sub-tasks done, 4/6 stories done</t>
+          <t>15/16 sub-tasks done, 5/6 stories done; refusal eval needs API keys on staging</t>
         </is>
       </c>
       <c r="P168" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="P169" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="P174" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P178" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12384,19 +12384,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N181" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N181" s="53" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O181" s="36" t="inlineStr">
         <is>
-          <t>eval not run</t>
+          <t>ready: demo corpus + 20/15 set (spike/retrieval-eval/demo), retrieval:seed-corpus, retrieval:eval --answer; needs OPENAI_API_KEY + ANTHROPIC_API_KEY on staging to run against the real models</t>
         </is>
       </c>
       <c r="P181" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12451,19 +12451,19 @@
           <t>p1,m3</t>
         </is>
       </c>
-      <c r="N182" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N182" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O182" s="36" t="inlineStr">
         <is>
-          <t>1/2 sub-tasks done</t>
+          <t>2/2 sub-tasks done</t>
         </is>
       </c>
       <c r="P182" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12522,12 +12522,12 @@
       </c>
       <c r="O183" s="36" t="inlineStr">
         <is>
-          <t>history passed to Answerer</t>
+          <t>Conversation::history — 6 turns / 6,000 chars / 1,500 per turn, access-checked; standalone query for retrieval</t>
         </is>
       </c>
       <c r="P183" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12579,19 +12579,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N184" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N184" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O184" s="36" t="inlineStr">
         <is>
-          <t>covered indirectly in RetrievalTest</t>
+          <t>ChatConversationTest: follow-up rewrite ([condense]), bounded history, no replay after access loss, scoped sessions, privacy, turn order</t>
         </is>
       </c>
       <c r="P184" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="P185" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="P188" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -12906,12 +12906,12 @@
       </c>
       <c r="O189" s="36" t="inlineStr">
         <is>
-          <t>normalised-text grouping; semantic grouping (FR-614) not built</t>
+          <t>grouped by meaning (FR-614): embeddings, cosine ≥ 0.8, labelled by most-asked phrasing with variants</t>
         </is>
       </c>
       <c r="P189" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18612,23 +18612,23 @@
         <v>16</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="36" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" s="54" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I11" s="36" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
     </row>
@@ -18818,16 +18818,16 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="55" t="n">
         <v>0.87</v>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 98 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 34 tests and the production build; CI confirmation pending the push</t>
+          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 106 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 34 tests and the production build; CI confirmation pending the push</t>
         </is>
       </c>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -13023,19 +13023,19 @@
           <t>epic</t>
         </is>
       </c>
-      <c r="N191" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N191" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O191" s="36" t="inlineStr">
         <is>
-          <t>8/10 sub-tasks done, 2/4 stories done</t>
+          <t>10/10 sub-tasks done, 4/4 stories done</t>
         </is>
       </c>
       <c r="P191" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13106,7 +13106,7 @@
       </c>
       <c r="P192" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13357,19 +13357,19 @@
           <t>p1,m4</t>
         </is>
       </c>
-      <c r="N196" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N196" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O196" s="36" t="inlineStr">
         <is>
-          <t>2/3 sub-tasks done</t>
+          <t>3/3 sub-tasks done</t>
         </is>
       </c>
       <c r="P196" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13544,19 +13544,19 @@
           <t>database</t>
         </is>
       </c>
-      <c r="N199" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N199" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O199" s="36" t="inlineStr">
         <is>
-          <t>translation_of is one-directional; no back-link list on the source yet</t>
+          <t>Document::source()/translations(); GET /documents/{id} and /published return source + translations (visible, published-only for readers); reader/editor links; assist panel blocks duplicate languages</t>
         </is>
       </c>
       <c r="P199" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13611,19 +13611,19 @@
           <t>p2,m4</t>
         </is>
       </c>
-      <c r="N200" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N200" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O200" s="36" t="inlineStr">
         <is>
-          <t>1/2 sub-tasks done</t>
+          <t>2/2 sub-tasks done</t>
         </is>
       </c>
       <c r="P200" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13739,19 +13739,19 @@
           <t>frontend</t>
         </is>
       </c>
-      <c r="N202" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N202" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O202" s="36" t="inlineStr">
         <is>
-          <t>reader + editor banner; document list indicator not added</t>
+          <t>reader banner + source link, editor banner + source link, space browser shows language tag and "out of date"</t>
         </is>
       </c>
       <c r="P202" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="P203" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18647,10 +18647,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="36" t="n">
         <v>0</v>
@@ -18659,11 +18659,11 @@
         <v>0</v>
       </c>
       <c r="H12" s="54" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I12" s="36" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/4</t>
         </is>
       </c>
     </row>
@@ -18818,10 +18818,10 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" s="39" t="n">
         <v>7</v>
@@ -18830,7 +18830,7 @@
         <v>11</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -15013,12 +15013,12 @@
       </c>
       <c r="O222" s="36" t="inlineStr">
         <is>
-          <t>9/11 sub-tasks done, 3/4 stories done</t>
+          <t>10/11 sub-tasks done, 3/4 stories done; only the payment-provider driver remains, blocked on the provider decision</t>
         </is>
       </c>
       <c r="P222" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15089,7 +15089,7 @@
       </c>
       <c r="P223" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15148,12 +15148,12 @@
       </c>
       <c r="O224" s="36" t="inlineStr">
         <is>
-          <t>superseded: counters computed live from tables (Billing\Usage), no separate tables</t>
+          <t>subscriptions table created (migration 001600, doc 04 v2.9); usage_counters superseded by live counters (Billing\Usage)</t>
         </is>
       </c>
       <c r="P224" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15333,12 +15333,12 @@
       </c>
       <c r="O227" s="36" t="inlineStr">
         <is>
-          <t>1/3 sub-tasks done</t>
+          <t>2/3 sub-tasks done</t>
         </is>
       </c>
       <c r="P227" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O228" s="36" t="inlineStr">
         <is>
-          <t>billing provider undecided</t>
+          <t>provider-independent part done: BillingProvider driver interface, subscriptions table, POST /billing/webhook (normalised events), Null + Fake drivers, app.yaml settings. The real driver is one class once the provider is chosen (open decision 03 §12)</t>
         </is>
       </c>
       <c r="P228" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15454,19 +15454,19 @@
           <t>backend</t>
         </is>
       </c>
-      <c r="N229" s="53" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="N229" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O229" s="36" t="inlineStr">
         <is>
-          <t>after provider</t>
+          <t>Plans: upgrade/more seats at once (provider prorates), downgrade/fewer seats scheduled at period end (billing:apply-scheduled hourly + webhook), refused with counts when over the new limits, Team &gt;10 seats refused (open decision); S22 plan chooser + seats + scheduled notice; PlanChangeTest</t>
         </is>
       </c>
       <c r="P229" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="P231" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -15860,7 +15860,7 @@
       </c>
       <c r="P235" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18717,7 +18717,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>0</v>
@@ -18726,10 +18726,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="54" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="I14" s="36" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E17" s="39" t="n">
         <v>5</v>
@@ -18827,10 +18827,10 @@
         <v>7</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 106 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 34 tests and the production build; CI confirmation pending the push</t>
+          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 110 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 34 tests and the production build; CI confirmation pending the push</t>
         </is>
       </c>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -16031,19 +16031,19 @@
           <t>epic</t>
         </is>
       </c>
-      <c r="N238" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N238" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O238" s="36" t="inlineStr">
         <is>
-          <t>4/8 sub-tasks done, 1/4 stories done</t>
+          <t>8/8 sub-tasks done, 4/4 stories done</t>
         </is>
       </c>
       <c r="P238" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16110,7 +16110,7 @@
       </c>
       <c r="P239" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16288,19 +16288,19 @@
           <t>p2,m5</t>
         </is>
       </c>
-      <c r="N242" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N242" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O242" s="36" t="inlineStr">
         <is>
-          <t>1/2 sub-tasks done</t>
+          <t>2/2 sub-tasks done</t>
         </is>
       </c>
       <c r="P242" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16416,19 +16416,19 @@
           <t>frontend</t>
         </is>
       </c>
-      <c r="N244" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N244" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O244" s="36" t="inlineStr">
         <is>
-          <t>past-review by space in insights; review-due notifications to owners; no owner dashboard</t>
+          <t>GET /analytics/past-review + list on Insights; GET /me/documents owner dashboard (/my-documents) with needs ranked most urgent first</t>
         </is>
       </c>
       <c r="P244" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16487,19 +16487,19 @@
           <t>p2,m5</t>
         </is>
       </c>
-      <c r="N245" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N245" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O245" s="36" t="inlineStr">
         <is>
-          <t>0/2 sub-tasks done</t>
+          <t>2/2 sub-tasks done</t>
         </is>
       </c>
       <c r="P245" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16551,14 +16551,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N246" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N246" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>retrieval:check-index every 10 min (built under G1-T5): re-queue, stray-chunk cleanup, admin notice</t>
         </is>
       </c>
       <c r="P246" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16610,14 +16615,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N247" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N247" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>`alerts` log channel (stderr + Slack at warning when LOG_SLACK_WEBHOOK_URL set); app.yaml platform alerts; infra/runbooks (index, billing, pipeline)</t>
         </is>
       </c>
       <c r="P247" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16676,19 +16686,19 @@
           <t>p2,m5</t>
         </is>
       </c>
-      <c r="N248" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N248" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O248" s="36" t="inlineStr">
         <is>
-          <t>1/2 sub-tasks done</t>
+          <t>2/2 sub-tasks done</t>
         </is>
       </c>
       <c r="P248" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16804,14 +16814,19 @@
           <t>backend</t>
         </is>
       </c>
-      <c r="N250" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N250" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>ops:cost-report [--month] [--csv]: per workspace pipeline $, $/SOP, chat $, assist $, plan price, margin %; chat_messages.cost_usd added</t>
         </is>
       </c>
       <c r="P250" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18752,23 +18767,23 @@
         <v>8</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I15" s="36" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>4/4</t>
         </is>
       </c>
     </row>
@@ -18818,19 +18833,19 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G17" s="39" t="n">
         <v>10</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>
@@ -18850,7 +18865,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 110 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 34 tests and the production build; CI confirmation pending the push</t>
+          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 113 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 35 tests and the production build; CI confirmation pending the push</t>
         </is>
       </c>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -16556,7 +16556,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O246" t="inlineStr">
+      <c r="O246" s="36" t="inlineStr">
         <is>
           <t>retrieval:check-index every 10 min (built under G1-T5): re-queue, stray-chunk cleanup, admin notice</t>
         </is>
@@ -16620,7 +16620,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O247" t="inlineStr">
+      <c r="O247" s="36" t="inlineStr">
         <is>
           <t>`alerts` log channel (stderr + Slack at warning when LOG_SLACK_WEBHOOK_URL set); app.yaml platform alerts; infra/runbooks (index, billing, pipeline)</t>
         </is>
@@ -16819,7 +16819,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O250" t="inlineStr">
+      <c r="O250" s="36" t="inlineStr">
         <is>
           <t>ops:cost-report [--month] [--csv]: per workspace pipeline $, $/SOP, chat $, assist $, plan price, margin %; chat_messages.cost_usd added</t>
         </is>
@@ -16881,12 +16881,12 @@
       </c>
       <c r="O251" s="36" t="inlineStr">
         <is>
-          <t>9/17 sub-tasks done, 1/5 stories done</t>
+          <t>16/17 sub-tasks done, 4/5 stories done; only provisioning in the DO account remains</t>
         </is>
       </c>
       <c r="P251" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16957,7 +16957,7 @@
       </c>
       <c r="P252" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17194,19 +17194,19 @@
           <t>p0,m0</t>
         </is>
       </c>
-      <c r="N256" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N256" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O256" s="36" t="inlineStr">
         <is>
-          <t>1/2 sub-tasks done</t>
+          <t>2/2 sub-tasks done</t>
         </is>
       </c>
       <c r="P256" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17322,19 +17322,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N258" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N258" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O258" s="36" t="inlineStr">
         <is>
-          <t>CD not configured</t>
+          <t>.github/workflows/deploy.yml: staging on green CI (doctl apps update --spec --wait, SENTRY_RELEASE stamped, smoke check); production from app.production.yaml behind the GitHub "production" environment gate; spec drift check in CI</t>
         </is>
       </c>
       <c r="P258" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17400,12 +17400,12 @@
       </c>
       <c r="O259" s="36" t="inlineStr">
         <is>
-          <t>2/4 sub-tasks done</t>
+          <t>3/4 sub-tasks done</t>
         </is>
       </c>
       <c r="P259" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17521,19 +17521,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N261" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N261" s="53" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="O261" s="36" t="inlineStr">
         <is>
-          <t>spec written; provisioning is an ops step</t>
+          <t>spec + provisioning runbook done (infra/runbooks/provisioning.md: managed MySQL/Valkey with TLS, trusted sources, FT setting, Spaces, secrets); needs the DO account to run it</t>
         </is>
       </c>
       <c r="P261" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17585,19 +17585,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N262" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N262" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O262" s="36" t="inlineStr">
         <is>
-          <t>pre-deploy migrate job; rollback drill not done</t>
+          <t>pre-deploy migrate job; rollback drill in CI on MySQL 8.4 (fresh → rollback 3 → migrate → reset → migrate); deploy-and-rollback runbook with per-migration down() impact</t>
         </is>
       </c>
       <c r="P262" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17716,19 +17716,19 @@
           <t>p1,m1</t>
         </is>
       </c>
-      <c r="N264" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N264" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O264" s="36" t="inlineStr">
         <is>
-          <t>0/4 sub-tasks done</t>
+          <t>4/4 sub-tasks done</t>
         </is>
       </c>
       <c r="P264" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17780,14 +17780,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N265" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N265" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>sentry/sentry-laravel (Integration::handles) + @sentry/angular loaded lazily behind a build-time DSN; release = commit via CD, environment tag; TrackingErrorHandler queues early errors</t>
         </is>
       </c>
       <c r="P265" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17839,19 +17844,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N266" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N266" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O266" s="36" t="inlineStr">
         <is>
-          <t>pipeline_jobs status/errors; structured stdout logging not added</t>
+          <t>`pipeline` log channel: one JSON line per stage event (started/succeeded/failed) with workspace, recording, stage, attempt, duration, cost</t>
         </is>
       </c>
       <c r="P266" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17903,14 +17908,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N267" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N267" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Ops\Metrics + GET /internal/metrics (bearer METRICS_TOKEN, Prometheus text): stage success/p50/p95, cost per SOP, index backlog, chat refusal/latency; infra/monitoring Grafana dashboard + rules</t>
         </is>
       </c>
       <c r="P267" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -17962,14 +17972,19 @@
           <t>infra</t>
         </is>
       </c>
-      <c r="N268" s="52" t="inlineStr">
-        <is>
-          <t>To Do</t>
+      <c r="N268" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>ops:check-health every 10 min: generation failure rate &gt; 25% (halts excluded), embedding backlog (&gt;10 docs, &gt;60 min, failed index jobs) → alerts channel, once an hour; unindexed docs via retrieval:check-index</t>
         </is>
       </c>
       <c r="P268" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18028,19 +18043,19 @@
           <t>p0,m0</t>
         </is>
       </c>
-      <c r="N269" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N269" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O269" s="36" t="inlineStr">
         <is>
-          <t>3/4 sub-tasks done</t>
+          <t>4/4 sub-tasks done</t>
         </is>
       </c>
       <c r="P269" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18269,19 +18284,19 @@
           <t>qa</t>
         </is>
       </c>
-      <c r="N273" s="51" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+      <c r="N273" s="43" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="O273" s="36" t="inlineStr">
         <is>
-          <t>visual check pending</t>
+          <t>contrast audited: white on review blue 6.9:1 / approved 6.0:1 AA; draft amber and archived grey pills switched to near-black text (5.5 / 6.8:1, white was 3.8 / 3.1); review blue never on navy (2.0:1); contrast.spec.ts enforces it</t>
         </is>
       </c>
       <c r="P273" s="36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -18802,23 +18817,23 @@
         <v>17</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="54" t="n">
-        <v>0.53</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I16" s="36" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>4/5</t>
         </is>
       </c>
     </row>
@@ -18833,19 +18848,19 @@
         <v>194</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E17" s="39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F17" s="39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="55" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I17" s="39" t="inlineStr"/>
     </row>
@@ -18865,7 +18880,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 113 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 35 tests and the production build; CI confirmation pending the push</t>
+          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 115 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 40 tests and the production build; CI confirmation pending the push</t>
         </is>
       </c>
     </row>

--- a/Documentation/jira-backlog.xlsx
+++ b/Documentation/jira-backlog.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jira Import" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progress" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epic Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestone Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Load" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Guide" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blocked — what unblocks it" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Epic Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestone Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Load" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Guide" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jira Import'!$A$1:$M$273</definedName>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -99,6 +100,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="9">
@@ -181,7 +186,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -405,6 +410,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5559,12 +5568,12 @@
       </c>
       <c r="O75" s="36" t="inlineStr">
         <is>
-          <t>17/22 sub-tasks done, 3/6 stories done; the rest need real recordings / provider keys</t>
+          <t>17/22 sub-tasks done, 3/6 stories done; remaining sub-tasks are Blocked (see 'Blocked — what unblocks it')</t>
         </is>
       </c>
       <c r="P75" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9874,12 @@
       </c>
       <c r="O142" s="36" t="inlineStr">
         <is>
-          <t>16/19 sub-tasks done, 3/6 stories done; the rest need the DO droplet and design-partner content</t>
+          <t>16/19 sub-tasks done, 3/6 stories done; remaining sub-tasks are Blocked (see 'Blocked — what unblocks it')</t>
         </is>
       </c>
       <c r="P142" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -11548,12 +11557,12 @@
       </c>
       <c r="O168" s="36" t="inlineStr">
         <is>
-          <t>15/16 sub-tasks done, 5/6 stories done; refusal eval needs API keys on staging</t>
+          <t>15/16 sub-tasks done, 5/6 stories done; remaining sub-tasks are Blocked (see 'Blocked — what unblocks it')</t>
         </is>
       </c>
       <c r="P168" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -15013,12 +15022,12 @@
       </c>
       <c r="O222" s="36" t="inlineStr">
         <is>
-          <t>10/11 sub-tasks done, 3/4 stories done; only the payment-provider driver remains, blocked on the provider decision</t>
+          <t>10/11 sub-tasks done, 3/4 stories done; remaining sub-tasks are Blocked (see 'Blocked — what unblocks it')</t>
         </is>
       </c>
       <c r="P222" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -16881,12 +16890,12 @@
       </c>
       <c r="O251" s="36" t="inlineStr">
         <is>
-          <t>16/17 sub-tasks done, 4/5 stories done; only provisioning in the DO account remains</t>
+          <t>16/17 sub-tasks done, 4/5 stories done; remaining sub-tasks are Blocked (see 'Blocked — what unblocks it')</t>
         </is>
       </c>
       <c r="P251" s="36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17794,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr">
+      <c r="O265" s="36" t="inlineStr">
         <is>
           <t>sentry/sentry-laravel (Integration::handles) + @sentry/angular loaded lazily behind a build-time DSN; release = commit via CD, environment tag; TrackingErrorHandler queues early errors</t>
         </is>
@@ -17913,7 +17922,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O267" t="inlineStr">
+      <c r="O267" s="36" t="inlineStr">
         <is>
           <t>Ops\Metrics + GET /internal/metrics (bearer METRICS_TOKEN, Prometheus text): stage success/p50/p95, cost per SOP, index backlog, chat refusal/latency; infra/monitoring Grafana dashboard + rules</t>
         </is>
@@ -17977,7 +17986,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr">
+      <c r="O268" s="36" t="inlineStr">
         <is>
           <t>ops:check-health every 10 min: generation failure rate &gt; 25% (halts excluded), embedding backlog (&gt;10 docs, &gt;60 min, failed index jobs) → alerts channel, once an hour; unindexed docs via retrieval:check-index</t>
         </is>
@@ -18331,7 +18340,7 @@
     <row r="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>Progress as of 2026-09-23 — derived from the Status column on 'Jira Import'</t>
+          <t>Progress as of 2026-09-24 — derived from the Status column on 'Jira Import'. CI on GitHub is green for commit 2dbd6f7 (all three jobs: API on SQLite, API on MySQL 8.4 incl. tenancy suite, rollback drill and real Qdrant, and web lint/test/build).</t>
         </is>
       </c>
     </row>
@@ -18880,7 +18889,7 @@
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>built, lint-clean, unit/feature tests written. As of 2026-09-23 the API passes the raw-query check, Pint, PHPStan level 6 and all 115 PHPUnit tests on SQLite and on MySQL 8.4 locally; the web app passes lint, 40 tests and the production build; CI confirmation pending the push</t>
+          <t>built, lint-clean, tests written and passing; confirmed by CI on GitHub for 2dbd6f7 (API 115 tests on SQLite and MySQL 8.4, PHPStan level 6, Pint, raw-query check, Qdrant integration, migration rollback drill; web lint, 40 tests, production build)</t>
         </is>
       </c>
     </row>
@@ -18916,7 +18925,7 @@
       </c>
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>waiting on a decision, keys or material from the team (transcription provider, billing provider, real recordings)</t>
+          <t>cannot be finished by development alone — needs a decision, an account, keys or real content from the team; see the 'Blocked — what unblocks it' sheet</t>
         </is>
       </c>
     </row>
@@ -18934,6 +18943,480 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" style="37" min="1" max="1"/>
+    <col width="6" customWidth="1" style="37" min="2" max="2"/>
+    <col width="34" customWidth="1" style="37" min="3" max="3"/>
+    <col width="52" customWidth="1" style="37" min="4" max="4"/>
+    <col width="60" customWidth="1" style="37" min="5" max="5"/>
+    <col width="22" customWidth="1" style="37" min="6" max="6"/>
+    <col width="52" customWidth="1" style="37" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="80" t="inlineStr">
+        <is>
+          <t>Blocked items as of 2026-09-24 — everything development could build is done; each row needs one thing from the team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C3" s="39" t="inlineStr">
+        <is>
+          <t>Sub-task</t>
+        </is>
+      </c>
+      <c r="D3" s="39" t="inlineStr">
+        <is>
+          <t>What is already built</t>
+        </is>
+      </c>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>What unblocks it</t>
+        </is>
+      </c>
+      <c r="F3" s="39" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Then run</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="81" t="inlineStr">
+        <is>
+          <t>D0-T1</t>
+        </is>
+      </c>
+      <c r="B4" s="81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C4" s="81" t="inlineStr">
+        <is>
+          <t>Assemble 10-recording evaluation set</t>
+        </is>
+      </c>
+      <c r="D4" s="81" t="inlineStr">
+        <is>
+          <t>eval-set.csv lists the 20 slots to cover; pipeline:eval runs them</t>
+        </is>
+      </c>
+      <c r="E4" s="81" t="inlineStr">
+        <is>
+          <t>10 real screen recordings, narrated, unscripted (spike/generation-eval/eval-set.csv slots 1–10)</t>
+        </is>
+      </c>
+      <c r="F4" s="81" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="G4" s="81" t="inlineStr">
+        <is>
+          <t>php artisan pipeline:eval &lt;folder&gt; --mock  (harness check), then with keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="81" t="inlineStr">
+        <is>
+          <t>D0-T2</t>
+        </is>
+      </c>
+      <c r="B5" s="81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" s="81" t="inlineStr">
+        <is>
+          <t>Benchmark Whisper API vs Deepgram</t>
+        </is>
+      </c>
+      <c r="D5" s="81" t="inlineStr">
+        <is>
+          <t>Both drivers, side-by-side run, cost and timestamp columns in runs.csv</t>
+        </is>
+      </c>
+      <c r="E5" s="81" t="inlineStr">
+        <is>
+          <t>OPENAI_API_KEY and DEEPGRAM_API_KEY on staging + the recordings above</t>
+        </is>
+      </c>
+      <c r="F5" s="81" t="inlineStr">
+        <is>
+          <t>Project lead</t>
+        </is>
+      </c>
+      <c r="G5" s="81" t="inlineStr">
+        <is>
+          <t>php artisan pipeline:eval &lt;folder&gt; --providers=whisper,deepgram; python score.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>D0-T3</t>
+        </is>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>Confirm zero-retention terms</t>
+        </is>
+      </c>
+      <c r="D6" s="81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="81" t="inlineStr">
+        <is>
+          <t>Choose the provider from the benchmark, then written confirmation from the vendor (BRD D5)</t>
+        </is>
+      </c>
+      <c r="F6" s="81" t="inlineStr">
+        <is>
+          <t>Project lead</t>
+        </is>
+      </c>
+      <c r="G6" s="81" t="inlineStr">
+        <is>
+          <t>set TRANSCRIPTION_DRIVER=whisper|deepgram in App Platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="81" t="inlineStr">
+        <is>
+          <t>D2-T4</t>
+        </is>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>Segmentation accuracy eval</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="inlineStr">
+        <is>
+          <t>segments-review.csv written per run; score.py reports boundary precision/recall/F1 ±2 s</t>
+        </is>
+      </c>
+      <c r="E7" s="81" t="inlineStr">
+        <is>
+          <t>The 20 recordings + a reviewer marking human boundaries</t>
+        </is>
+      </c>
+      <c r="F7" s="81" t="inlineStr">
+        <is>
+          <t>Team + reviewer</t>
+        </is>
+      </c>
+      <c r="G7" s="81" t="inlineStr">
+        <is>
+          <t>python spike/generation-eval/score.py --out &lt;out&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="81" t="inlineStr">
+        <is>
+          <t>D4-T5</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>Generation eval set (20 recordings)</t>
+        </is>
+      </c>
+      <c r="D8" s="81" t="inlineStr">
+        <is>
+          <t>pipeline:eval writes draft.md, frames, metrics; human-review.csv per run</t>
+        </is>
+      </c>
+      <c r="E8" s="81" t="inlineStr">
+        <is>
+          <t>The 20 recordings + a reviewer filling human-review.csv (verdict, step count, frames ok)</t>
+        </is>
+      </c>
+      <c r="F8" s="81" t="inlineStr">
+        <is>
+          <t>Team + reviewer</t>
+        </is>
+      </c>
+      <c r="G8" s="81" t="inlineStr">
+        <is>
+          <t>python spike/generation-eval/score.py --out &lt;out&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="81" t="inlineStr">
+        <is>
+          <t>G0-T2</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>Stand up Qdrant on DigitalOcean</t>
+        </is>
+      </c>
+      <c r="D9" s="81" t="inlineStr">
+        <is>
+          <t>infra/qdrant: compose (v1.19.1 + Caddy TLS), cloud-init, nightly snapshots, runbook; QdrantStore proven against real Qdrant in CI</t>
+        </is>
+      </c>
+      <c r="E9" s="81" t="inlineStr">
+        <is>
+          <t>Create droplet, volume, DNS and firewall in the DO account (infra/qdrant/README.md steps 1–5); set QDRANT_URL / QDRANT_API_KEY / OPENAI_API_KEY in App Platform</t>
+        </is>
+      </c>
+      <c r="F9" s="81" t="inlineStr">
+        <is>
+          <t>Ops (DO account owner)</t>
+        </is>
+      </c>
+      <c r="G9" s="81" t="inlineStr">
+        <is>
+          <t>php artisan vector:ensure-collection; php artisan retrieval:check-index --dry-run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="81" t="inlineStr">
+        <is>
+          <t>G2-T3</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>Relevance eval set (50 + 15 questions)</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>retrieval:eval harness, demo corpus + demo set, retrieval:seed-corpus, doc 08 targets in summary.md</t>
+        </is>
+      </c>
+      <c r="E10" s="81" t="inlineStr">
+        <is>
+          <t>Design-partner content and 50 answerable + 15 unanswerable questions in spike/retrieval-eval format</t>
+        </is>
+      </c>
+      <c r="F10" s="81" t="inlineStr">
+        <is>
+          <t>Project lead + design partner</t>
+        </is>
+      </c>
+      <c r="G10" s="81" t="inlineStr">
+        <is>
+          <t>php artisan retrieval:eval set.json --workspace=&lt;slug&gt; --as=&lt;email&gt; --answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="81" t="inlineStr">
+        <is>
+          <t>G3-T3</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>Ranking quality eval</t>
+        </is>
+      </c>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t>retrieval:eval compares fusion weights side by side (--weights)</t>
+        </is>
+      </c>
+      <c r="E11" s="81" t="inlineStr">
+        <is>
+          <t>The eval set from G2-T3</t>
+        </is>
+      </c>
+      <c r="F11" s="81" t="inlineStr">
+        <is>
+          <t>Project lead</t>
+        </is>
+      </c>
+      <c r="G11" s="81" t="inlineStr">
+        <is>
+          <t>php artisan retrieval:eval ... --weights=1:0.6,1:0.3,1:1,1:0,0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>H3-T3</t>
+        </is>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>Refusal eval (15 unanswerable questions)</t>
+        </is>
+      </c>
+      <c r="D12" s="81" t="inlineStr">
+        <is>
+          <t>demo/set.json has 15 unanswerable; --answer checks assistant refusal + citations</t>
+        </is>
+      </c>
+      <c r="E12" s="81" t="inlineStr">
+        <is>
+          <t>OPENAI_API_KEY + ANTHROPIC_API_KEY on staging, demo corpus seeded</t>
+        </is>
+      </c>
+      <c r="F12" s="81" t="inlineStr">
+        <is>
+          <t>Project lead</t>
+        </is>
+      </c>
+      <c r="G12" s="81" t="inlineStr">
+        <is>
+          <t>retrieval:seed-corpus demo/corpus.json ...; retrieval:eval demo/set.json ... --answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>K2-T1</t>
+        </is>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="inlineStr">
+        <is>
+          <t>Payment provider integration and webhooks</t>
+        </is>
+      </c>
+      <c r="D13" s="81" t="inlineStr">
+        <is>
+          <t>BillingProvider interface, subscriptions table, plan-change rules, scheduled downgrades, webhook endpoint, Null + Fake drivers, S22 plan chooser</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="inlineStr">
+        <is>
+          <t>Decide the provider (Stripe / Paddle / …) — open decision 03 §12; then one driver class implementing BillingProvider</t>
+        </is>
+      </c>
+      <c r="F13" s="81" t="inlineStr">
+        <is>
+          <t>CEO / project lead</t>
+        </is>
+      </c>
+      <c r="G13" s="81" t="inlineStr">
+        <is>
+          <t>set BILLING_DRIVER=&lt;provider&gt;, BILLING_WEBHOOK_SECRET; run PlanChangeTest against the real driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>M3-T2</t>
+        </is>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C14" s="81" t="inlineStr">
+        <is>
+          <t>Managed MySQL and Valkey with TLS</t>
+        </is>
+      </c>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t>app.yaml + app.production.yaml, provisioning runbook, CD workflow, rollback drill</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
+          <t>Run infra/runbooks/provisioning.md in the DO account; add GitHub secrets DIGITALOCEAN_ACCESS_TOKEN, DO_STAGING_APP_ID, DO_PRODUCTION_APP_ID and the "production" environment with reviewers</t>
+        </is>
+      </c>
+      <c r="F14" s="81" t="inlineStr">
+        <is>
+          <t>Ops (DO account owner)</t>
+        </is>
+      </c>
+      <c r="G14" s="81" t="inlineStr">
+        <is>
+          <t>re-run the Deploy workflow (it failed at doctl auth on 23 Sep because the token is not set yet)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19540,7 +20023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19822,7 +20305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20037,7 +20520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
